--- a/canada-strong/_data/canada_strong_content_review.xlsx
+++ b/canada-strong/_data/canada_strong_content_review.xlsx
@@ -135,7 +135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -154,7 +154,7 @@
     <row r="3" spans="1:1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">This workbook has two working tabs plus this one.</t>
+          <t xml:space="preserve">Last checked against the source files on 2026-09-03.</t>
         </is>
       </c>
     </row>
@@ -162,199 +162,199 @@
       <c r="A4" s="12"/>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This workbook has two working tabs plus this one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="12"/>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">TAB: Content Review</t>
         </is>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="8" spans="1:1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  One row per piece of interface text (questions, labels, headings, body copy),</t>
         </is>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="9" spans="1:1">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  English next to French. Use this tab to comment on wording, tone, or translation.</t>
         </is>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="12"/>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="11" t="inlineStr">
+    <row r="10" spans="1:1">
+      <c r="A10" s="12"/>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">TAB: Decision Tree</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Shows which selections lead to which results. The wizard has 4 questions - Need,</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Region, Size, Sector - and the results page is built from several independent</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  blocks of content. Each block is driven by only one or two of the four questions;</t>
+          <t xml:space="preserve">  Shows which selections lead to which results. The wizard has 4 questions - Need,</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  the other questions do not change that block, and are marked (any).</t>
+          <t xml:space="preserve">  Region, Size, Sector - and the results page is built from several independent</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="12"/>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  blocks of content. Each block is driven by only one or two of the four questions;</t>
+        </is>
+      </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The blocks, in the order they appear on the results page:</t>
+          <t xml:space="preserve">  the other questions do not change that block, and are marked (any).</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1. Sector-specific programs      - depends on Need + Sector</t>
-        </is>
-      </c>
+      <c r="A16" s="12"/>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2. Sector-agnostic programs      - depends on Need only (always shown)</t>
+          <t xml:space="preserve">  Note: Question 2 (region) now has 7 answers, not 6 - Ontario was split into</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3. Regional programs             - depends on Need + Region</t>
+          <t xml:space="preserve">  Northern Ontario and Southern Ontario, each its own answer with its own RDA link,</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4. Sector hub links              - depends on Sector only</t>
+          <t xml:space="preserve">  because FedNor and FedDev Ontario are two separate agencies. The Prairies answer</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5. Always-on hub links           - shown on every path, no matter what</t>
+          <t xml:space="preserve">  was also relabelled to "Manitoba, Saskatchewan, Alberta" (same region underneath).</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    6. Eligibility - fixed criteria  - always the same, regardless of answers</t>
-        </is>
-      </c>
+      <c r="A21" s="12"/>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    7. Eligibility badges by size    - depends on Size (Q3) only</t>
+          <t xml:space="preserve">  The blocks, in the order they appear on the results page:</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    8. Eligibility badge by sector   - depends on Sector (Q4) only</t>
+          <t xml:space="preserve">    1. Sector-specific programs      - depends on Need + Sector</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="12"/>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2. Sector-agnostic programs      - depends on Need only (always shown)</t>
+        </is>
+      </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  To trace one full click-through: pick a Need + Sector row in block 1 (the main</t>
+          <t xml:space="preserve">    3. Regional programs             - depends on Need + Region</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  program panel), then read the matching Need row in block 2, the matching</t>
+          <t xml:space="preserve">    4. Sector hub links              - depends on Sector only</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Need + Region row in block 3, the matching Sector row in block 4, block 5 as-is,</t>
+          <t xml:space="preserve">    5. Always-on hub links           - shown on every path, no matter what</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  and the matching Size row in block 7 plus Sector row in block 8. Together those</t>
+          <t xml:space="preserve">    6. Eligibility - fixed criteria  - always the same, regardless of answers</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  give everything shown on that path.</t>
+          <t xml:space="preserve">    7. Eligibility badges by size    - depends on Size (Q3) only</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="12"/>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    8. Eligibility badge by sector   - depends on Sector (Q4) only</t>
+        </is>
+      </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Use the Comments column here to flag routing that looks wrong (a program missing</t>
+          <t xml:space="preserve">    9. Eligibility panel - RDA note  - depends on Region (Q2) only (new)</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  or misplaced for a given selection), separate from wording issues in Content Review.</t>
-        </is>
-      </c>
+      <c r="A32" s="12"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="12"/>
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Note: as of 2026-09-03, a sector + need combination with no matching program</t>
+        </is>
+      </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Both tabs: set Status to Needs change if flagging something for a fix, or Approved</t>
+          <t xml:space="preserve">  (block 1) shows nothing at all - the old "No stream specific to your sector"</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">once happy with a row. Leave as Open otherwise. Add your name under Reviewer.</t>
+          <t xml:space="preserve">  notice was removed. Those rows are marked "(nothing shown here)" below.</t>
         </is>
       </c>
     </row>
@@ -362,35 +362,138 @@
       <c r="A36" s="12"/>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Source files:</t>
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Note: block 9 is new - once any region is picked, a one-line note naming that</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/canada_strong_en.yml</t>
+          <t xml:space="preserve">  region's development agency (with a link) is appended at the bottom of the</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/canada_strong_fr.yml</t>
+          <t xml:space="preserve">  Eligibility criteria panel, after the checklist and the Large Enterprise note.</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  It does not depend on Need, Size, or Sector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="12"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  To trace one full click-through: pick a Need + Sector row in block 1 (the main</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  program panel), then read the matching Need row in block 2, the matching</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Need + Region row in block 3, the matching Sector row in block 4, block 5 as-is,</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the matching Size row in block 7, Sector row in block 8, and Region row in block 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Together those give everything shown on that path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="12"/>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Use the Comments column here to flag routing that looks wrong (a program missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  or misplaced for a given selection), separate from wording issues in Content Review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="12"/>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Both tabs: set Status to Needs change if flagging something for a fix, or Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">once happy with a row. Leave as Open otherwise. Add your name under Reviewer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="12"/>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source files:</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/canada_strong_en.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/canada_strong_fr.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">  canada-strong/_data/tariff_tool_links.csv  (the program list behind the Decision Tree tab)</t>
         </is>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="12" t="inlineStr">
+    <row r="58" spans="1:1">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  canada-strong/business-en.html  (the template that assembles the results page)</t>
         </is>
@@ -402,7 +505,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -744,22 +847,22 @@
     <row r="12" spans="1:7">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start page</t>
+          <t xml:space="preserve">Regions (regional development agency name)</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start.title</t>
+          <t xml:space="preserve">regions.reg-atl.rda</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find support for tariff impacts</t>
+          <t xml:space="preserve">Atlantic Canada Opportunities Agency</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trouver du soutien face aux droits de douane</t>
+          <t xml:space="preserve">Agence de promotion économique du Canada atlantique</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -773,22 +876,22 @@
     <row r="13" spans="1:7">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start page</t>
+          <t xml:space="preserve">Regions (regional development agency name)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start.description</t>
+          <t xml:space="preserve">regions.reg-qc.rda</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the federal supports available to businesses, employers and workers affected by United States tariffs.</t>
+          <t xml:space="preserve">Canada Economic Development for Quebec Regions</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trouvez les mesures de soutien fédérales offertes aux entreprises, aux employeurs et aux travailleurs touchés par les droits de douane américains.</t>
+          <t xml:space="preserve">Développement économique Canada pour les régions du Québec</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -802,22 +905,22 @@
     <row r="14" spans="1:7">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start page</t>
+          <t xml:space="preserve">Regions (regional development agency name)</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start.h1</t>
+          <t xml:space="preserve">regions.reg-on-n.rda</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find support for tariff impacts</t>
+          <t xml:space="preserve">Federal Economic Development Agency for Northern Ontario</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trouver du soutien face aux droits de douane</t>
+          <t xml:space="preserve">Agence fédérale de développement économique pour le Nord de l'Ontario</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -831,22 +934,22 @@
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start page</t>
+          <t xml:space="preserve">Regions (regional development agency name)</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start.intro</t>
+          <t xml:space="preserve">regions.reg-on-s.rda</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the support you need</t>
+          <t xml:space="preserve">Federal Economic Development Agency for Southern Ontario</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trouvez le soutien qu'il vous faut</t>
+          <t xml:space="preserve">Agence fédérale de développement économique pour le Sud de l'Ontario</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -860,22 +963,22 @@
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start page</t>
+          <t xml:space="preserve">Regions (regional development agency name)</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start.options[0].label</t>
+          <t xml:space="preserve">regions.reg-pr.rda</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">I am a business or employer</t>
+          <t xml:space="preserve">Prairies Economic Development Canada</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Je suis une entreprise ou un employeur</t>
+          <t xml:space="preserve">Développement économique Canada pour les Prairies</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -889,22 +992,22 @@
     <row r="17" spans="1:7">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start page</t>
+          <t xml:space="preserve">Regions (regional development agency name)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start.options[0].description</t>
+          <t xml:space="preserve">regions.reg-bc.rda</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer four questions about need, region, size and sector</t>
+          <t xml:space="preserve">PacifiCan</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Répondez à quatre questions sur votre besoin, votre région, votre taille et votre secteur</t>
+          <t xml:space="preserve">PacifiCan</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -918,22 +1021,22 @@
     <row r="18" spans="1:7">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start page</t>
+          <t xml:space="preserve">Regions (regional development agency name)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start.options[0].cta</t>
+          <t xml:space="preserve">regions.reg-nor.rda</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Build me a short list</t>
+          <t xml:space="preserve">Canadian Northern Economic Development Agency</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dressez ma liste</t>
+          <t xml:space="preserve">Agence canadienne de développement économique du Nord</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -945,198 +1048,198 @@
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Start page</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start.options[1].label</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I am a worker</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis un travailleur ou une travailleuse</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="2"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start.title</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Find support for tariff impacts</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trouver du soutien face aux droits de douane</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F19" s="9"/>
+      <c r="G19" s="6"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Start page</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start.options[1].description</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reach income support, skills training and student aid directly</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Accédez directement au soutien du revenu, à la formation et à l'aide aux étudiants</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="2"/>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start.description</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Find the federal supports available to businesses, employers and workers affected by United States tariffs.</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trouvez les mesures de soutien fédérales offertes aux entreprises, aux employeurs et aux travailleurs touchés par les droits de douane américains.</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F20" s="9"/>
+      <c r="G20" s="6"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Start page</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start.options[1].cta</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Show me worker supports</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Montrez-moi le soutien aux travailleurs</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="2"/>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start.h1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Find support for tariff impacts</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trouver du soutien face aux droits de douane</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="G21" s="6"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Start page</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start.options[2].label</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I want more information</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je veux plus d'information</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="2"/>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start.intro</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Find the support you need</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trouvez le soutien qu'il vous faut</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F22" s="9"/>
+      <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Start page</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start.options[2].description</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">General overview of Canada's response to U.S. tariffs</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aperçu général de la réponse du Canada aux droits de douane américains</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="2"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start.options[0].label</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I am a business or employer</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis une entreprise ou un employeur</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F23" s="9"/>
+      <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Start page</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start.options[2].cta</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Give me the overview</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Donnez-moi l'aperçu</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="2"/>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start.options[0].description</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answer four questions about need, region, size and sector</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Répondez à quatre questions sur votre besoin, votre région, votre taille et votre secteur</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F24" s="9"/>
+      <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Business wizard - general</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Start page</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.title</t>
+          <t xml:space="preserve">start.options[0].cta</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find support for your business</t>
+          <t xml:space="preserve">Build me a short list</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trouver du soutien pour votre entreprise</t>
+          <t xml:space="preserve">Dressez ma liste</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -1150,22 +1253,22 @@
     <row r="26" spans="1:7">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - general</t>
+          <t xml:space="preserve">Start page</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.description</t>
+          <t xml:space="preserve">start.options[1].label</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer four questions to get a shortlist of federal programs for businesses affected by United States tariffs.</t>
+          <t xml:space="preserve">I am a worker</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Répondez à quatre questions pour obtenir une liste de programmes fédéraux destinés aux entreprises touchées par les droits de douane américains.</t>
+          <t xml:space="preserve">Je suis un travailleur ou une travailleuse</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -1179,22 +1282,22 @@
     <row r="27" spans="1:7">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - general</t>
+          <t xml:space="preserve">Start page</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.h1</t>
+          <t xml:space="preserve">start.options[1].description</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find support for your business</t>
+          <t xml:space="preserve">Reach income support, skills training and student aid directly</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trouver du soutien pour votre entreprise</t>
+          <t xml:space="preserve">Accédez directement au soutien du revenu, à la formation et à l'aide aux étudiants</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -1208,22 +1311,22 @@
     <row r="28" spans="1:7">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - general</t>
+          <t xml:space="preserve">Start page</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.intro</t>
+          <t xml:space="preserve">start.options[1].cta</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer four questions and we will show you the programs that fit your need, your region, your size and your sector.</t>
+          <t xml:space="preserve">Show me worker supports</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Répondez à quatre questions et nous vous montrerons les programmes qui correspondent à votre besoin, à votre région, à votre taille et à votre secteur.</t>
+          <t xml:space="preserve">Montrez-moi le soutien aux travailleurs</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1237,22 +1340,22 @@
     <row r="29" spans="1:7">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - general</t>
+          <t xml:space="preserve">Start page</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.questions_heading</t>
+          <t xml:space="preserve">start.options[2].label</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tell us about your business</t>
+          <t xml:space="preserve">I want more information</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parlez-nous de votre entreprise</t>
+          <t xml:space="preserve">Je veux plus d'information</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -1266,22 +1369,22 @@
     <row r="30" spans="1:7">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - general</t>
+          <t xml:space="preserve">Start page</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.results_heading</t>
+          <t xml:space="preserve">start.options[2].description</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programs that match your answers</t>
+          <t xml:space="preserve">General overview of Canada's response to U.S. tariffs</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programmes correspondant à vos réponses</t>
+          <t xml:space="preserve">Aperçu général de la réponse du Canada aux droits de douane américains</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -1295,22 +1398,22 @@
     <row r="31" spans="1:7">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - general</t>
+          <t xml:space="preserve">Start page</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.back_link</t>
+          <t xml:space="preserve">start.options[2].cta</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start over</t>
+          <t xml:space="preserve">Give me the overview</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recommencer</t>
+          <t xml:space="preserve">Donnez-moi l'aperçu</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -1324,22 +1427,22 @@
     <row r="32" spans="1:7">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - result labels</t>
+          <t xml:space="preserve">Business wizard - general</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.agnostic_suffix</t>
+          <t xml:space="preserve">business.title</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">open to all sectors</t>
+          <t xml:space="preserve">Find support for your business</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">tous secteurs confondus</t>
+          <t xml:space="preserve">Trouver du soutien pour votre entreprise</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -1353,22 +1456,22 @@
     <row r="33" spans="1:7">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - result labels</t>
+          <t xml:space="preserve">Business wizard - general</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.route_heading</t>
+          <t xml:space="preserve">business.description</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No stream specific to your sector</t>
+          <t xml:space="preserve">Answer four questions to get a shortlist of federal programs for businesses affected by United States tariffs.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aucun volet propre à votre secteur</t>
+          <t xml:space="preserve">Répondez à quatre questions pour obtenir une liste de programmes fédéraux destinés aux entreprises touchées par les droits de douane américains.</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -1382,22 +1485,22 @@
     <row r="34" spans="1:7">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - result labels</t>
+          <t xml:space="preserve">Business wizard - general</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.route_body</t>
+          <t xml:space="preserve">business.h1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no program stream built for your sector and this need. The programs below are open to all sectors and are where you should start.</t>
+          <t xml:space="preserve">Find support for your business</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il n'existe pas de volet conçu pour votre secteur et ce besoin. Les programmes ci-dessous sont ouverts à tous les secteurs et constituent votre point de départ.</t>
+          <t xml:space="preserve">Trouver du soutien pour votre entreprise</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -1411,22 +1514,22 @@
     <row r="35" spans="1:7">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - result labels</t>
+          <t xml:space="preserve">Business wizard - general</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.region_heading</t>
+          <t xml:space="preserve">business.intro</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programs for your region</t>
+          <t xml:space="preserve">Answer four questions and we will show you the programs that fit your need, your region, your size and your sector.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programmes pour votre région</t>
+          <t xml:space="preserve">Répondez à quatre questions et nous vous montrerons les programmes qui correspondent à votre besoin, à votre région, à votre taille et à votre secteur.</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -1440,22 +1543,22 @@
     <row r="36" spans="1:7">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - result labels</t>
+          <t xml:space="preserve">Business wizard - general</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.region_footnote</t>
+          <t xml:space="preserve">business.questions_heading</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional criteria and intake dates vary.</t>
+          <t xml:space="preserve">Tell us about your business</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les critères régionaux et les dates de réception des demandes varient.</t>
+          <t xml:space="preserve">Parlez-nous de votre entreprise</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -1469,22 +1572,22 @@
     <row r="37" spans="1:7">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - result labels</t>
+          <t xml:space="preserve">Business wizard - general</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.hub_heading</t>
+          <t xml:space="preserve">business.results_heading</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Where these programs are listed</t>
+          <t xml:space="preserve">Programs that match your answers</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Où ces programmes sont répertoriés</t>
+          <t xml:space="preserve">Programmes correspondant à vos réponses</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -1498,22 +1601,22 @@
     <row r="38" spans="1:7">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business wizard - result labels</t>
+          <t xml:space="preserve">Business wizard - general</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.labels.hub_body</t>
+          <t xml:space="preserve">business.back_link</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">These hubs are the departments' own lists. They are kept current, so check them if something here looks out of date.</t>
+          <t xml:space="preserve">Start over</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ces carrefours sont les listes tenues par les ministères eux-mêmes. Ils sont à jour : consultez-les si une information ici semble désuète.</t>
+          <t xml:space="preserve">Recommencer</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -1527,22 +1630,22 @@
     <row r="39" spans="1:7">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 1 - need</t>
+          <t xml:space="preserve">Business wizard - result labels</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.questions.question-1.legend</t>
+          <t xml:space="preserve">business.labels.agnostic_suffix</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 1 of 4: What do you need right now?</t>
+          <t xml:space="preserve">open to all sectors</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 1 sur 4 : De quoi avez-vous besoin en ce moment?</t>
+          <t xml:space="preserve">tous secteurs confondus</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -1556,22 +1659,22 @@
     <row r="40" spans="1:7">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 1 - need</t>
+          <t xml:space="preserve">Business wizard - result labels</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-1.option[need-fin]</t>
+          <t xml:space="preserve">business.labels.region_heading</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Financing to keep operating or grow</t>
+          <t xml:space="preserve">Programs for your region</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du financement pour poursuivre vos activités ou prendre de l'expansion</t>
+          <t xml:space="preserve">Programmes pour votre région</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -1585,22 +1688,22 @@
     <row r="41" spans="1:7">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 1 - need</t>
+          <t xml:space="preserve">Business wizard - result labels</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-1.option[need-liq]</t>
+          <t xml:space="preserve">business.labels.region_footnote</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+          <t xml:space="preserve">Regional criteria and intake dates vary.</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Des liquidités pour combler un manque de trésorerie causé par les droits de douane</t>
+          <t xml:space="preserve">Les critères régionaux et les dates de réception des demandes varient.</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -1614,22 +1717,22 @@
     <row r="42" spans="1:7">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 1 - need</t>
+          <t xml:space="preserve">Business wizard - result labels</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-1.option[need-tra]</t>
+          <t xml:space="preserve">business.labels.hub_heading</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformation or capital project</t>
+          <t xml:space="preserve">Where these programs are listed</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Un projet de transformation ou d'immobilisations</t>
+          <t xml:space="preserve">Où ces programmes sont répertoriés</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -1643,22 +1746,22 @@
     <row r="43" spans="1:7">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 1 - need</t>
+          <t xml:space="preserve">Business wizard - result labels</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-1.option[need-wrk]</t>
+          <t xml:space="preserve">business.labels.hub_body</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
+          <t xml:space="preserve">These hubs are the departments' own lists. They are kept current, so check them if something here looks out of date.</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Le maintien en poste et le recyclage de votre main-d'œuvre</t>
+          <t xml:space="preserve">Ces carrefours sont les listes tenues par les ministères eux-mêmes. Ils sont à jour : consultez-les si une information ici semble désuète.</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -1670,53 +1773,53 @@
       <c r="G43" s="6"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 2 - region</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">business.questions.question-2.legend</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 2 of 4: Where is your business located?</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 2 sur 4 : Où votre entreprise est-elle située?</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F44" s="5"/>
-      <c r="G44" s="2"/>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business wizard - result labels</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">business.labels.rda_prefix</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: </t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : </t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F44" s="9"/>
+      <c r="G44" s="6"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 2 - region</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 1 - need</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-atl]</t>
+          <t xml:space="preserve">business.questions.question-1.legend</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlantic</t>
+          <t xml:space="preserve">Question 1 of 4: What do you need right now?</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlantique</t>
+          <t xml:space="preserve">Question 1 sur 4 : De quoi avez-vous besoin en ce moment?</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -1730,22 +1833,22 @@
     <row r="46" spans="1:7">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 2 - region</t>
+          <t xml:space="preserve">Question 1 - need</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-qc]</t>
+          <t xml:space="preserve">question-1.option[need-fin]</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quebec</t>
+          <t xml:space="preserve">Financing to keep operating or grow</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Québec</t>
+          <t xml:space="preserve">Du financement pour poursuivre vos activités ou prendre de l'expansion</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -1759,22 +1862,22 @@
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 2 - region</t>
+          <t xml:space="preserve">Question 1 - need</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-on]</t>
+          <t xml:space="preserve">question-1.option[need-liq]</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ontario</t>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ontario</t>
+          <t xml:space="preserve">Des liquidités pour combler un manque de trésorerie causé par les droits de douane</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -1788,22 +1891,22 @@
     <row r="48" spans="1:7">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 2 - region</t>
+          <t xml:space="preserve">Question 1 - need</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-pr]</t>
+          <t xml:space="preserve">question-1.option[need-tra]</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prairies</t>
+          <t xml:space="preserve">Transformation or capital project</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prairies</t>
+          <t xml:space="preserve">Un projet de transformation ou d'immobilisations</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -1817,22 +1920,22 @@
     <row r="49" spans="1:7">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 2 - region</t>
+          <t xml:space="preserve">Question 1 - need</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-2.option[reg-bc]</t>
+          <t xml:space="preserve">question-1.option[need-wrk]</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Workforce retention and retraining</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colombie-Britannique</t>
+          <t xml:space="preserve">Le maintien en poste et le recyclage de votre main-d'œuvre</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -1844,53 +1947,53 @@
       <c r="G49" s="2"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 2 - region</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question-2.option[reg-nor]</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The North</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Le Nord</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F50" s="5"/>
-      <c r="G50" s="2"/>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">business.questions.question-2.legend</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 2 of 4: Where is your business located?</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 2 sur 4 : Où votre entreprise est-elle située?</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F50" s="9"/>
+      <c r="G50" s="6"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 3 - size</t>
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 2 - region</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.questions.question-3.legend</t>
+          <t xml:space="preserve">question-2.option[reg-atl]</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 3 of 4: What is your size and revenue?</t>
+          <t xml:space="preserve">Atlantic</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 3 sur 4 : Quels sont votre taille et vos revenus?</t>
+          <t xml:space="preserve">Atlantique</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -1904,22 +2007,22 @@
     <row r="52" spans="1:7">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 3 - size</t>
+          <t xml:space="preserve">Question 2 - region</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-under1m]</t>
+          <t xml:space="preserve">question-2.option[reg-qc]</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under $1 million in annual revenue</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moins de 1 million de dollars de revenus annuels</t>
+          <t xml:space="preserve">Québec</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -1933,22 +2036,22 @@
     <row r="53" spans="1:7">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 3 - size</t>
+          <t xml:space="preserve">Question 2 - region</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-1to5m]</t>
+          <t xml:space="preserve">question-2.option[reg-on-n]</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">De 1 à 5 millions de dollars et 3 ans ou plus d'activité</t>
+          <t xml:space="preserve">Nord de l'Ontario (y compris Parry Sound)</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -1962,22 +2065,22 @@
     <row r="54" spans="1:7">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 3 - size</t>
+          <t xml:space="preserve">Question 2 - region</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-5mplus]</t>
+          <t xml:space="preserve">question-2.option[reg-on-s]</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
+          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 millions de dollars ou plus et 10 employés à temps plein ou plus</t>
+          <t xml:space="preserve">Sud de l'Ontario (au sud de Muskoka)</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -1991,22 +2094,22 @@
     <row r="55" spans="1:7">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 3 - size</t>
+          <t xml:space="preserve">Question 2 - region</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-large]</t>
+          <t xml:space="preserve">question-2.option[reg-pr]</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Large enterprise</t>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grande entreprise</t>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -2018,82 +2121,82 @@
       <c r="G55" s="6"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 4 - sector</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">business.questions.question-4.legend</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 4 of 4: What is your sector and tariff impact?</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 4 sur 4 : Quel est votre secteur et quelle est l'incidence des droits de douane?</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F56" s="5"/>
-      <c r="G56" s="2"/>
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 2 - region</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-2.option[reg-bc]</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">British Columbia</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colombie-Britannique</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F56" s="9"/>
+      <c r="G56" s="6"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 4 - sector</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question-4.option[sec-forestry]</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forestry and softwood lumber</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Foresterie et bois d'œuvre</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F57" s="5"/>
-      <c r="G57" s="2"/>
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 2 - region</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-2.option[reg-nor]</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The North</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le Nord</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F57" s="9"/>
+      <c r="G57" s="6"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 4 - sector</t>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 3 - size</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-steel]</t>
+          <t xml:space="preserve">business.questions.question-3.legend</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steel, aluminium and copper</t>
+          <t xml:space="preserve">Question 3 of 4: What is your size and revenue?</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acier, aluminium et cuivre</t>
+          <t xml:space="preserve">Question 3 sur 4 : Quels sont votre taille et vos revenus?</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -2107,22 +2210,22 @@
     <row r="59" spans="1:7">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 4 - sector</t>
+          <t xml:space="preserve">Question 3 - size</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-mfg]</t>
+          <t xml:space="preserve">question-3.option[size-under1m]</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
+          <t xml:space="preserve">Under $1 million in annual revenue</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabrication et autres exportateurs</t>
+          <t xml:space="preserve">Moins de 1 million de dollars de revenus annuels</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -2136,22 +2239,22 @@
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 4 - sector</t>
+          <t xml:space="preserve">Question 3 - size</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-agri]</t>
+          <t xml:space="preserve">question-3.option[size-1to5m]</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agroalimentaire, poisson et fruits de mer</t>
+          <t xml:space="preserve">De 1 à 5 millions de dollars et 3 ans ou plus d'activité</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -2165,22 +2268,22 @@
     <row r="61" spans="1:7">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Question 4 - sector</t>
+          <t xml:space="preserve">Question 3 - size</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-usexport]</t>
+          <t xml:space="preserve">question-3.option[size-5mplus]</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exportations vers les États-Unis représentant 15 % ou plus de vos revenus</t>
+          <t xml:space="preserve">5 millions de dollars ou plus et 10 employés à temps plein ou plus</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -2192,53 +2295,53 @@
       <c r="G61" s="2"/>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility checklist</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">business.eligibility.heading</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Critères d'admissibilité</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F62" s="9"/>
-      <c r="G62" s="6"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 3 - size</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-3.option[size-large]</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large enterprise</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grande entreprise</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F62" s="5"/>
+      <c r="G62" s="2"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility checklist</t>
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.eligibility.body</t>
+          <t xml:space="preserve">business.questions.question-4.legend</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programs on this page commonly apply these criteria. This is a guide, not a decision - the program you apply to makes the final determination.</t>
+          <t xml:space="preserve">Question 4 of 4: What is your sector and tariff impact?</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les programmes de cette page appliquent couramment ces critères. Il s'agit d'un guide et non d'une décision : le programme auquel vous présentez une demande rend la décision finale.</t>
+          <t xml:space="preserve">Question 4 sur 4 : Quel est votre secteur et quelle est l'incidence des droits de douane?</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -2252,22 +2355,22 @@
     <row r="64" spans="1:7">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility checklist</t>
+          <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[0].text (incorporation)</t>
+          <t xml:space="preserve">question-4.option[sec-forestry]</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Canadian-incorporated</t>
+          <t xml:space="preserve">Forestry and softwood lumber</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Constituée en société au Canada</t>
+          <t xml:space="preserve">Foresterie et bois d'œuvre</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -2281,22 +2384,22 @@
     <row r="65" spans="1:7">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility checklist</t>
+          <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[1].text (years operating)</t>
+          <t xml:space="preserve">question-4.option[sec-steel]</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 or more years operating</t>
+          <t xml:space="preserve">Steel, aluminium and copper</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 ans ou plus d'activité</t>
+          <t xml:space="preserve">Acier, aluminium et cuivre</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -2310,22 +2413,22 @@
     <row r="66" spans="1:7">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility checklist</t>
+          <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[2].text (revenue)</t>
+          <t xml:space="preserve">question-4.option[sec-mfg]</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$1 million or more in annual revenue</t>
+          <t xml:space="preserve">Manufacturing and other exporters</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 million de dollars ou plus de revenus annuels</t>
+          <t xml:space="preserve">Fabrication et autres exportateurs</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -2339,22 +2442,22 @@
     <row r="67" spans="1:7">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility checklist</t>
+          <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[3].text (cash flow)</t>
+          <t xml:space="preserve">question-4.option[sec-agri]</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive cash flow</t>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flux de trésorerie positif</t>
+          <t xml:space="preserve">Agriculture, agroalimentaire, poisson et fruits de mer</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -2368,22 +2471,22 @@
     <row r="68" spans="1:7">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility checklist</t>
+          <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[4].text (US export/tariff impact)</t>
+          <t xml:space="preserve">question-4.option[sec-usexport]</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15% or more of revenue from U.S. exports, or a 10% tariff-driven revenue decline or cost increase</t>
+          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 % ou plus des revenus provenant d'exportations vers les États-Unis, ou une baisse de revenus ou une hausse de coûts de 10 % attribuable aux droits de douane</t>
+          <t xml:space="preserve">Exportations vers les États-Unis représentant 15 % ou plus de vos revenus</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -2395,53 +2498,53 @@
       <c r="G68" s="6"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility checklist</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">business.eligibility.large_note</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">As a large enterprise, the Large Enterprise Tariff Loan (LETL) is the stream built for your size.</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">En tant que grande entreprise, le Crédit pour les grandes entreprises touchées par les droits de douane est le volet conçu pour votre taille.</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F69" s="9"/>
-      <c r="G69" s="6"/>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">business.eligibility.heading</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critères d'admissibilité</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F69" s="5"/>
+      <c r="G69" s="2"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility badges</t>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility checklist</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">badge[met] (years/revenue/US export)</t>
+          <t xml:space="preserve">business.eligibility.body</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Met</t>
+          <t xml:space="preserve">Programs on this page commonly apply these criteria. This is a guide, not a decision - the program you apply to makes the final determination.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Satisfait</t>
+          <t xml:space="preserve">Les programmes de cette page appliquent couramment ces critères. Il s'agit d'un guide et non d'une décision : le programme auquel vous présentez une demande rend la décision finale.</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -2455,22 +2558,22 @@
     <row r="71" spans="1:7">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility badges</t>
+          <t xml:space="preserve">Eligibility checklist</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">badge[review] (incorporation/years/cash flow/US export)</t>
+          <t xml:space="preserve">criteria[0].text (incorporation)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Needs review</t>
+          <t xml:space="preserve">Canadian-incorporated</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">À vérifier</t>
+          <t xml:space="preserve">Constituée en société au Canada</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -2484,22 +2587,22 @@
     <row r="72" spans="1:7">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eligibility badges</t>
+          <t xml:space="preserve">Eligibility checklist</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">badge[notmet] (revenue)</t>
+          <t xml:space="preserve">criteria[1].text (years operating)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not met</t>
+          <t xml:space="preserve">3 or more years operating</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non satisfait</t>
+          <t xml:space="preserve">3 ans ou plus d'activité</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -2510,10 +2613,213 @@
       <c r="F72" s="5"/>
       <c r="G72" s="2"/>
     </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility checklist</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">criteria[2].text (revenue)</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$1 million or more in annual revenue</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 million de dollars ou plus de revenus annuels</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F73" s="5"/>
+      <c r="G73" s="2"/>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility checklist</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">criteria[3].text (cash flow)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive cash flow</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flux de trésorerie positif</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F74" s="5"/>
+      <c r="G74" s="2"/>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility checklist</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">criteria[4].text (US export/tariff impact)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15% or more of revenue from U.S. exports, or a 10% tariff-driven revenue decline or cost increase</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 % ou plus des revenus provenant d'exportations vers les États-Unis, ou une baisse de revenus ou une hausse de coûts de 10 % attribuable aux droits de douane</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F75" s="5"/>
+      <c r="G75" s="2"/>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility checklist</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">business.eligibility.large_note</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As a large enterprise, the Large Enterprise Tariff Loan (LETL) is the stream built for your size.</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En tant que grande entreprise, le Crédit pour les grandes entreprises touchées par les droits de douane est le volet conçu pour votre taille.</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F76" s="5"/>
+      <c r="G76" s="2"/>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility badges</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badge[met] (years/revenue/US export)</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Met</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Satisfait</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F77" s="9"/>
+      <c r="G77" s="6"/>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility badges</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badge[review] (incorporation/years/cash flow/US export)</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs review</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À vérifier</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F78" s="9"/>
+      <c r="G78" s="6"/>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility badges</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badge[notmet] (revenue)</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not met</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non satisfait</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F79" s="9"/>
+      <c r="G79" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G72"/>
+  <autoFilter ref="A1:G79"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E72">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E79">
       <formula1>"Open,Needs change,Approved"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2522,16 +2828,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
     <col min="6" max="6" width="32" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
     <col min="8" max="8" width="46" customWidth="1"/>
     <col min="9" max="9" width="46" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
@@ -2634,17 +2940,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Route notice: "No stream specific to your sector"</t>
+          <t xml:space="preserve">(nothing shown here)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no program stream built for your sector and this need. The programs below are open to all sectors and are where you should start.</t>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il n'existe pas de volet conçu pour votre secteur et ce besoin. Les programmes ci-dessous sont ouverts à tous les secteurs et constituent votre point de départ.</t>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -2688,17 +2994,17 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Route notice: "No stream specific to your sector"</t>
+          <t xml:space="preserve">(nothing shown here)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no program stream built for your sector and this need. The programs below are open to all sectors and are where you should start.</t>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il n'existe pas de volet conçu pour votre secteur et ce besoin. Les programmes ci-dessous sont ouverts à tous les secteurs et constituent votre point de départ.</t>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
@@ -3246,17 +3552,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Route notice: "No stream specific to your sector"</t>
+          <t xml:space="preserve">(nothing shown here)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no program stream built for your sector and this need. The programs below are open to all sectors and are where you should start.</t>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il n'existe pas de volet conçu pour votre secteur et ce besoin. Les programmes ci-dessous sont ouverts à tous les secteurs et constituent votre point de départ.</t>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -3470,17 +3776,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Route notice: "No stream specific to your sector"</t>
+          <t xml:space="preserve">(nothing shown here)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no program stream built for your sector and this need. The programs below are open to all sectors and are where you should start.</t>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il n'existe pas de volet conçu pour votre secteur et ce besoin. Les programmes ci-dessous sont ouverts à tous les secteurs et constituent votre point de départ.</t>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -3524,17 +3830,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Route notice: "No stream specific to your sector"</t>
+          <t xml:space="preserve">(nothing shown here)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no program stream built for your sector and this need. The programs below are open to all sectors and are where you should start.</t>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il n'existe pas de volet conçu pour votre secteur et ce besoin. Les programmes ci-dessous sont ouverts à tous les secteurs et constituent votre point de départ.</t>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -3632,17 +3938,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Route notice: "No stream specific to your sector"</t>
+          <t xml:space="preserve">(nothing shown here)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">There is no program stream built for your sector and this need. The programs below are open to all sectors and are where you should start.</t>
+          <t xml:space="preserve">(none - as of the 2026-09-03 update, an empty sector match shows no panel and no notice at all; it simply is not rendered)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Il n'existe pas de volet conçu pour votre secteur et ce besoin. Les programmes ci-dessous sont ouverts à tous les secteurs et constituent votre point de départ.</t>
+          <t xml:space="preserve">(aucun - depuis la mise à jour du 2026-09-03, une absence de correspondance sectorielle n'affiche plus aucun encadré ni aucun avis; rien n'est affiché)</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -4077,7 +4383,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ontario</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -4131,7 +4437,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prairies</t>
+          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -4185,7 +4491,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4239,7 +4545,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The North</t>
+          <t xml:space="preserve">British Columbia</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4288,12 +4594,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+          <t xml:space="preserve">Financing to keep operating or grow</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlantic</t>
+          <t xml:space="preserve">The North</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4308,17 +4614,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programs for your region</t>
+          <t xml:space="preserve">(no regional panel)</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Atlantic (ACOA / APECA)</t>
+          <t xml:space="preserve">(none - financing has no region-specific program)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire au Canada atlantique (ACOA / APECA)</t>
+          <t xml:space="preserve">(aucun - le financement n'a pas de programme régional)</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -4347,7 +4653,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quebec</t>
+          <t xml:space="preserve">Atlantic</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4367,12 +4673,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Quebec (CED / DEC)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Atlantic (ACOA / APECA)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Québec (CED / DEC)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire au Canada atlantique (ACOA / APECA)</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -4401,7 +4707,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ontario</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4421,14 +4727,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Southern Ontario (FedDev Ontario)
-Regional Tariff Response Initiative - Northern Ontario (FedNor)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Quebec (CED / DEC)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire dans le Sud de l'Ontario (FedDev Ontario)
-Initiative régionale de réponse tarifaire – Nord de l'Ontario (FedNor)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Québec (CED / DEC)</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -4457,7 +4761,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prairies</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4477,12 +4781,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Prairies (PrairiesCan)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Northern Ontario (FedNor)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire (IRRT) pour la région des Prairies (PrairiesCan)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord de l'Ontario (FedNor)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -4511,7 +4815,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4531,12 +4835,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - British Columbia (PacifiCan)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Southern Ontario (FedDev Ontario)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire en Colombie-Britannique (PacifiCan)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire dans le Sud de l'Ontario (FedDev Ontario)</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -4565,7 +4869,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The North</t>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4585,12 +4889,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - North (CanNor)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Prairies (PrairiesCan)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord (CanNor)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire (IRRT) pour la région des Prairies (PrairiesCan)</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -4614,12 +4918,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformation or capital project</t>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlantic</t>
+          <t xml:space="preserve">British Columbia</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4639,12 +4943,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Atlantic (ACOA / APECA)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - British Columbia (PacifiCan)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire au Canada atlantique (ACOA / APECA)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire en Colombie-Britannique (PacifiCan)</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
@@ -4668,12 +4972,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformation or capital project</t>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quebec</t>
+          <t xml:space="preserve">The North</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4693,12 +4997,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Quebec (CED / DEC)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - North (CanNor)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Québec (CED / DEC)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord (CanNor)</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -4727,7 +5031,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ontario</t>
+          <t xml:space="preserve">Atlantic</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4747,14 +5051,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Southern Ontario (FedDev Ontario)
-Regional Tariff Response Initiative - Northern Ontario (FedNor)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Atlantic (ACOA / APECA)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire dans le Sud de l'Ontario (FedDev Ontario)
-Initiative régionale de réponse tarifaire – Nord de l'Ontario (FedNor)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire au Canada atlantique (ACOA / APECA)</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -4783,7 +5085,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prairies</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4803,12 +5105,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - Prairies (PrairiesCan)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Quebec (CED / DEC)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire (IRRT) pour la région des Prairies (PrairiesCan)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Québec (CED / DEC)</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -4837,7 +5139,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4857,12 +5159,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - British Columbia (PacifiCan)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Northern Ontario (FedNor)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire en Colombie-Britannique (PacifiCan)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord de l'Ontario (FedNor)</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -4891,7 +5193,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The North</t>
+          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4911,12 +5213,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regional Tariff Response Initiative - North (CanNor)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Southern Ontario (FedDev Ontario)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord (CanNor)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire dans le Sud de l'Ontario (FedDev Ontario)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -4940,12 +5242,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
+          <t xml:space="preserve">Transformation or capital project</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlantic</t>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4960,17 +5262,17 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no regional panel)</t>
+          <t xml:space="preserve">Programs for your region</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - Prairies (PrairiesCan)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire (IRRT) pour la région des Prairies (PrairiesCan)</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -4994,12 +5296,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
+          <t xml:space="preserve">Transformation or capital project</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quebec</t>
+          <t xml:space="preserve">British Columbia</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5014,17 +5316,17 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no regional panel)</t>
+          <t xml:space="preserve">Programs for your region</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - British Columbia (PacifiCan)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire en Colombie-Britannique (PacifiCan)</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -5048,12 +5350,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workforce retention and retraining</t>
+          <t xml:space="preserve">Transformation or capital project</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ontario</t>
+          <t xml:space="preserve">The North</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5068,17 +5370,17 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no regional panel)</t>
+          <t xml:space="preserve">Programs for your region</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
+          <t xml:space="preserve">Regional Tariff Response Initiative - North (CanNor)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
+          <t xml:space="preserve">Initiative régionale de réponse tarifaire – Nord (CanNor)</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -5107,7 +5409,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prairies</t>
+          <t xml:space="preserve">Atlantic</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5161,7 +5463,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5215,7 +5517,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The North</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5252,935 +5554,935 @@
       <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Regional programs</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need + Q2 Region</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workforce retention and retraining</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no regional panel)</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K50" s="5"/>
+      <c r="L50" s="2"/>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Regional programs</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need + Q2 Region</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workforce retention and retraining</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no regional panel)</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K51" s="5"/>
+      <c r="L51" s="2"/>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Regional programs</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need + Q2 Region</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workforce retention and retraining</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">British Columbia</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no regional panel)</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K52" s="5"/>
+      <c r="L52" s="2"/>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Regional programs</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q1 Need + Q2 Region</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workforce retention and retraining</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The North</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no regional panel)</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(none - workforce has no region-specific program)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(aucun - la main-d'œuvre n'a pas de programme régional)</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K53" s="5"/>
+      <c r="L53" s="2"/>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Sector hub links</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Forestry and softwood lumber</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Forestry and lumber: where these programs are listed</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Support for forest sector employers and workers (hub) (NRCan)</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Soutien fédéral aux entreprises et aux travailleurs du secteur forestier (NRCan)</t>
         </is>
       </c>
-      <c r="J50" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K50" s="9"/>
-      <c r="L50" s="6"/>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K54" s="9"/>
+      <c r="L54" s="6"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Sector hub links</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Steel, aluminium and copper</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Steel and aluminum: where these programs are listed</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Support for the Canadian steel sector (Finance Canada)</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Soutien au secteur canadien de l'acier (Finance Canada)</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K51" s="9"/>
-      <c r="L51" s="6"/>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K55" s="9"/>
+      <c r="L55" s="6"/>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Sector hub links</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Manufacturing and other exporters</t>
         </is>
       </c>
-      <c r="G52" s="6" t="inlineStr">
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(no sector hub)</t>
         </is>
       </c>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(none)</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(aucun)</t>
         </is>
       </c>
-      <c r="J52" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K52" s="9"/>
-      <c r="L52" s="6"/>
-    </row>
-    <row r="53" spans="1:12">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K56" s="9"/>
+      <c r="L56" s="6"/>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Sector hub links</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Agriculture: where these programs are listed</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">AgPal / AgriGuichet (AAFC, third-party hosted)
 Support measures for industries affected by trade disruptions (hub) (AAFC)</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">AgriGuichet (AAFC, hébergé par un tiers)
 Mesures de soutien pour les industries touchées par les perturbations commerciales (AAFC)</t>
         </is>
       </c>
-      <c r="J53" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K53" s="9"/>
-      <c r="L53" s="6"/>
-    </row>
-    <row r="54" spans="1:12">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K57" s="9"/>
+      <c r="L57" s="6"/>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Sector hub links</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 Sector only (always shown for that sector)</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(no sector hub)</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(none)</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(aucun)</t>
         </is>
       </c>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K54" s="9"/>
-      <c r="L54" s="6"/>
-    </row>
-    <row r="55" spans="1:12">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K58" s="9"/>
+      <c r="L58" s="6"/>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">5. Always-on hub links</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">None - shown on every path</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Where these programs are listed</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Benefits Finder (ISED)
 Supports for business (hub) (ISED)
-Support for Canadian workers and employers (UPSTREAM HUB) (Finance Canada)</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
+Support for Canadian workers and employers (Finance Canada)</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Outil de recherche d'aide aux entreprises (ISED)
 Soutien aux entreprises (ISED)
 Soutien aux employeurs et aux travailleurs canadiens en réponse aux droits de douane (Finance Canada)</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K55" s="5"/>
-      <c r="L55" s="2"/>
-    </row>
-    <row r="56" spans="1:12">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K59" s="5"/>
+      <c r="L59" s="2"/>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">6. Eligibility - fixed criteria</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">None - always the same badge</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr">
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">"Canadian-incorporated" badge: Needs review</t>
         </is>
       </c>
-      <c r="I56" s="6" t="inlineStr">
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « Constituée en société au Canada » : À vérifier</t>
         </is>
       </c>
-      <c r="J56" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K56" s="9"/>
-      <c r="L56" s="6"/>
-    </row>
-    <row r="57" spans="1:12">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K60" s="9"/>
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">6. Eligibility - fixed criteria</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">None - always the same badge</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">"Positive cash flow" badge: Needs review</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
+      <c r="I61" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « Flux de trésorerie positif » : À vérifier</t>
         </is>
       </c>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K57" s="9"/>
-      <c r="L57" s="6"/>
-    </row>
-    <row r="58" spans="1:12">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K61" s="9"/>
+      <c r="L61" s="6"/>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Eligibility badges by size</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Q3 Size only</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Under $1 million in annual revenue</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"3 or more years operating" badge: Needs review
 "$1 million or more in annual revenue" badge: Not met
 Large Enterprise (LETL) note: not shown</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
 Insigne pour « 1 million de dollars ou plus de revenus annuels » : Non satisfait
 Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée</t>
         </is>
       </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K58" s="5"/>
-      <c r="L58" s="2"/>
-    </row>
-    <row r="59" spans="1:12">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K62" s="5"/>
+      <c r="L62" s="2"/>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Eligibility badges by size</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Q3 Size only</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"3 or more years operating" badge: Met
 "$1 million or more in annual revenue" badge: Met
 Large Enterprise (LETL) note: not shown</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : Satisfait
 Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
 Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée</t>
         </is>
       </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K59" s="5"/>
-      <c r="L59" s="2"/>
-    </row>
-    <row r="60" spans="1:12">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K63" s="5"/>
+      <c r="L63" s="2"/>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Eligibility badges by size</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Q3 Size only</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"3 or more years operating" badge: Needs review
 "$1 million or more in annual revenue" badge: Met
 Large Enterprise (LETL) note: not shown</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
 Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
 Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée</t>
         </is>
       </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K60" s="5"/>
-      <c r="L60" s="2"/>
-    </row>
-    <row r="61" spans="1:12">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K64" s="5"/>
+      <c r="L64" s="2"/>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Eligibility badges by size</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Q3 Size only</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Large enterprise</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"3 or more years operating" badge: Needs review
 "$1 million or more in annual revenue" badge: Met
 Large Enterprise (LETL) note: SHOWN - "As a large enterprise, the Large Enterprise Tariff Loan (LETL) is the stream built for your size."</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
 Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
 Note sur le Crédit pour les grandes entreprises (CGETDD) : AFFICHÉE - « En tant que grande entreprise, le Crédit pour les grandes entreprises touchées par les droits de douane est le volet conçu pour votre taille. »</t>
         </is>
       </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K61" s="5"/>
-      <c r="L61" s="2"/>
-    </row>
-    <row r="62" spans="1:12">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K65" s="5"/>
+      <c r="L65" s="2"/>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">8. Eligibility badge by sector</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 Sector only</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Forestry and softwood lumber</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
+      <c r="I66" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
-        </is>
-      </c>
-      <c r="J62" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K62" s="9"/>
-      <c r="L62" s="6"/>
-    </row>
-    <row r="63" spans="1:12">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Steel, aluminium and copper</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
-        </is>
-      </c>
-      <c r="J63" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K63" s="9"/>
-      <c r="L63" s="6"/>
-    </row>
-    <row r="64" spans="1:12">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
-        </is>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
-        </is>
-      </c>
-      <c r="J64" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K64" s="9"/>
-      <c r="L64" s="6"/>
-    </row>
-    <row r="65" spans="1:12">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
-        </is>
-      </c>
-      <c r="J65" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K65" s="9"/>
-      <c r="L65" s="6"/>
-    </row>
-    <row r="66" spans="1:12">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Met</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : Satisfait</t>
         </is>
       </c>
       <c r="J66" s="9" t="inlineStr">
@@ -6191,10 +6493,604 @@
       <c r="K66" s="9"/>
       <c r="L66" s="6"/>
     </row>
+    <row r="67" spans="1:12">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Eligibility badge by sector</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 Sector only</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Steel, aluminium and copper</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K67" s="9"/>
+      <c r="L67" s="6"/>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Eligibility badge by sector</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 Sector only</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manufacturing and other exporters</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K68" s="9"/>
+      <c r="L68" s="6"/>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Eligibility badge by sector</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 Sector only</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K69" s="9"/>
+      <c r="L69" s="6"/>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Eligibility badge by sector</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 Sector only</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Met</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : Satisfait</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K70" s="9"/>
+      <c r="L70" s="6"/>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atlantic</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: Atlantic Canada Opportunities Agency</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence de promotion économique du Canada atlantique</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K71" s="5"/>
+      <c r="L71" s="2"/>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quebec</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: Canada Economic Development for Quebec Regions</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Développement économique Canada pour les régions du Québec</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K72" s="5"/>
+      <c r="L72" s="2"/>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: Federal Economic Development Agency for Northern Ontario</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence fédérale de développement économique pour le Nord de l'Ontario</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K73" s="5"/>
+      <c r="L73" s="2"/>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: Federal Economic Development Agency for Southern Ontario</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence fédérale de développement économique pour le Sud de l'Ontario</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K74" s="5"/>
+      <c r="L74" s="2"/>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: Prairies Economic Development Canada</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Développement économique Canada pour les Prairies</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K75" s="5"/>
+      <c r="L75" s="2"/>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">British Columbia</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: PacifiCan</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : PacifiCan</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K76" s="5"/>
+      <c r="L76" s="2"/>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The North</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: Canadian Northern Economic Development Agency</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence canadienne de développement économique du Nord</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K77" s="5"/>
+      <c r="L77" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L66"/>
+  <autoFilter ref="A1:L77"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J66">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J77">
       <formula1>"Open,Needs change,Approved"</formula1>
     </dataValidation>
   </dataValidations>

--- a/canada-strong/_data/canada_strong_content_review.xlsx
+++ b/canada-strong/_data/canada_strong_content_review.xlsx
@@ -5,6 +5,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Content Review" sheetId="2" r:id="rId2"/>
     <sheet name="Decision Tree" sheetId="3" r:id="rId4"/>
+    <sheet name="Gap Analysis" sheetId="4" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -135,7 +136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A58"/>
+  <dimension ref="A1:A81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -164,7 +165,7 @@
     <row r="5" spans="1:1">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">This workbook has two working tabs plus this one.</t>
+          <t xml:space="preserve">This workbook has three working tabs plus this one.</t>
         </is>
       </c>
     </row>
@@ -448,54 +449,207 @@
       <c r="A50" s="12"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Both tabs: set Status to Needs change if flagging something for a fix, or Approved</t>
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAB: Gap Analysis</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">once happy with a row. Leave as Open otherwise. Add your name under Reviewer.</t>
+          <t xml:space="preserve">  Compares every program named on two live Canada.ca pages - the workers/employers</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="12"/>
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  tariff-support page and the Canada Strong campaign page - against the CSV that</t>
+        </is>
+      </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Source files:</t>
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  drives the wizard, to catch anything the wizard is missing.</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/canada_strong_en.yml</t>
+          <t xml:space="preserve">    1. Missing - employer/business side       - on the source page, not in the CSV</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/canada_strong_fr.yml</t>
+          <t xml:space="preserve">    2. Missing - new program (not in the CSV) - Build Communities Strong Fund</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/tariff_tool_links.csv  (the program list behind the Decision Tree tab)</t>
+          <t xml:space="preserve">    3. Missing - worker-facing supports        - out of scope by design: the wizard</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">                                                 only covers the business path, and</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 "I am a worker" on the start page</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 routes straight to that source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 instead of building a list</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    4. Confirmed present                       - already in the wizard; Maps to</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 wizard program names the matching</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 CSV / Decision Tree entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Set Status per row to Add to wizard, Won't add, or leave Open for a call still</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  to be made; rows already in the wizard default to Already covered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="12"/>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Content Review and Decision Tree tabs: set Status to Needs change if flagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">something for a fix, or Approved once happy with a row. Leave as Open otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add your name under Reviewer on any tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="12"/>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source files:</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/canada_strong_en.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/canada_strong_fr.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/tariff_tool_links.csv  (the program list behind the Decision Tree tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">  canada-strong/business-en.html  (the template that assembles the results page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="12"/>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Compared against, for the Gap Analysis tab (checked 2026-09-03):</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  https://www.canada.ca/en/department-finance/programs/international-trade-finance-policy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    canadas-response-us-tariffs/support-canadian-workers-employers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  https://www.canada.ca/en/campaign/canadastrong.html</t>
         </is>
       </c>
     </row>
@@ -7095,4 +7249,1339 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Program / Service</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organization</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Description (from source page)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source page</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maps to wizard program</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reviewer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Missing - employer/business side</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank (ESDC)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resources to help find, hire and retain the right workers, explore the job market and stay informed about employment standards.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Missing - employer/business side</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank - Training Finder</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank (ESDC)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For employers with a Work-Sharing agreement: training and other resources via Job Bank's Training Finder.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Missing - employer/business side</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank - Worker Search Tool</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank (ESDC)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Search an occupation to discover the number of workers looking for a job locally or nationwide.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Missing - employer/business side</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Expanding your business into new markets</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International Canada</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New market entry, reducing risk, trade data and inclusive trade.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(distinct from EDC's Market diversification guide, which IS in the wizard)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Missing - employer/business side</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What importers need to know</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CBSA</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resources for businesses importing goods into Canada.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Missing - employer/business side</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting Canadian exporters</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trade Commissioner Service (GAC)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Explore available resources to navigate U.S. tariffs.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(distinct page from "Support for Canadian exporters faced with U.S. tariffs", which IS in the wizard as the TCS row)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Missing - new program (not in the CSV at all)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build Communities Strong Fund</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(not stated on page)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investing in a wide range of infrastructure projects that support economic prosperity through housing, health, transit, and climate adaptation.</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canada Strong campaign page</t>
+        </is>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporary Employment Insurance (EI) Measures</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measures that improve access to EI benefits, including waiving the one-week EI waiting period.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank (worker-facing)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank (ESDC)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job postings and career opportunities - the leading source for jobs and labour market information.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skills for Success</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Government of Canada</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assess your skills and learn about the skills necessary to succeed in today's evolving labour market.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Training Finder (worker-facing)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Bank (ESDC)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gain in-demand skills from training courses by recognized Canadian institutions.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skills and employment training for Indigenous people</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Develop your skills and access job training through Indigenous service organizations.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canada Student Grants and Loans</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Government of Canada</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grants and loans available to full-time and part-time post-secondary students.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repayment Assistance Plan (RAP)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Government of Canada</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repayment assistance if you are having trouble paying your student loan.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Employment Insurance (EI) and courses or training programs</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Take a course or training program while receiving EI benefits.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canada Apprentice Loan</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Government of Canada</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interest-free loans to help complete an apprenticeship in a designated Red Seal trade.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tax deductions and credits for apprentices</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Government of Canada</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tax deductions and credits for tradespeople, including moving expenses, tuition fees and tool expenses.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Missing - worker-facing supports (out of scope by design)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EI for apprentices</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Income support during full-time technical training.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work-Sharing Program</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measures for employers experiencing a temporary reduction in business.</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work-Sharing Program (ESDC) - workforce, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H20" s="9"/>
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Student Work Placement Program</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wage subsidies to hire post-secondary students.</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Student Work Placement Program (ESDC) - workforce, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H21" s="9"/>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Worker Retention Grant</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Income support for EI-eligible employees on reduced hours under an approved Work-Sharing agreement.</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Worker Retention Grant (ESDC) - workforce, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H22" s="9"/>
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regional Tariff Response Initiative</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regional development agencies</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financial support for small and medium-sized enterprises impacted by tariffs.</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Both pages</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regional Tariff Response Initiative (national hub, liquidity/transformation agnostic) + per-region variants in the regional programs block</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H23" s="9"/>
+      <c r="I23" s="6"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strategic Response Fund</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISED</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For innovative projects in sectors affected by the U.S. tariffs.</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strategic Response Fund (SRF) (ISED) - transformation, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H24" s="9"/>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large Enterprise Tariff Loan</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEEFC</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loans for large Canadian enterprises affected by current and future tariffs and countermeasures.</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) (CEEFC / CDEV) - liquidity, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H25" s="9"/>
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supports for business</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISED</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loans, grants and tailored programs to help a business expand into new markets.</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supports for business (hub) (ISED) - always-on hub</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H26" s="9"/>
+      <c r="I26" s="6"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business Benefits Finder</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISED</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A tailored list of benefits that may be helpful to your business.</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business Benefits Finder (ISED) - always-on hub</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H27" s="9"/>
+      <c r="I27" s="6"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Process for requesting remission of tariffs</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finance Canada</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Request exceptional relief from tariffs imposed as part of Canada's countermeasures.</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Process for requesting remission of tariffs (Finance Canada) - liquidity, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H28" s="9"/>
+      <c r="I28" s="6"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support for the Canadian Steel Sector</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finance Canada</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trade measures, financial support and more to help the steel sector.</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support for the Canadian steel sector (Finance Canada) - steel sector hub</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H29" s="9"/>
+      <c r="I29" s="6"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support for forest sector</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Natural Resources Canada</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity support, assistance to affected workers and industry transformation.</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support for forest sector employers and workers (hub) (NRCan) - forestry sector hub</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H30" s="9"/>
+      <c r="I30" s="6"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duties Relief Program</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CBSA</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qualified businesses can apply to import commercial goods without paying duties.</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duties Relief Program (CBSA) - liquidity, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H31" s="9"/>
+      <c r="I31" s="6"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drawback Program</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CBSA</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removing the domestic duty impact from commercial goods to compete in export markets.</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duty Drawback Program (CBSA) - liquidity, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H32" s="9"/>
+      <c r="I32" s="6"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support for Canadian exporters faced with U.S. tariffs</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trade Commissioner Service (GAC)</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Help on how to export duty-free to the U.S.</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TCS - US tariffs support for exporters (GAC) - transformation, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H33" s="9"/>
+      <c r="I33" s="6"/>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Employment Insurance-funded Labour Market Development Agreements (LMDAs)</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESDC</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Government investments through LMDAs to help workers and employers affected by tariffs access training and employment support.</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workforce Tariff Response - EI-funded LMDAs (ESDC) - workforce, sector-agnostic</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H34" s="9"/>
+      <c r="I34" s="6"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Confirmed present - already covered</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Services for agri-food exporters (partial match)</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AAFC</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Help for agri-food businesses to export goods - trade shows, in-market expertise and the Canada Brand.</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workers-employers page</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canada Brand (AAFC) + Trade Commissioner Service (agri-food) (AAFC) - agriculture, transformation block</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already covered</t>
+        </is>
+      </c>
+      <c r="H35" s="9"/>
+      <c r="I35" s="6"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I35"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G35">
+      <formula1>"Open,Add to wizard,Won't add,Already covered"</formula1>
+    </dataValidation>
+  </dataValidations>
+</worksheet>
 </file>
--- a/canada-strong/_data/canada_strong_content_review.xlsx
+++ b/canada-strong/_data/canada_strong_content_review.xlsx
@@ -136,7 +136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A81"/>
+  <dimension ref="A1:A93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -155,7 +155,7 @@
     <row r="3" spans="1:1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Last checked against the source files on 2026-09-03.</t>
+          <t xml:space="preserve">Last checked against the source files on 2026-09-03 (commit 04ebf3ee, business size).</t>
         </is>
       </c>
     </row>
@@ -331,323 +331,403 @@
     <row r="31" spans="1:1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    9. Eligibility panel - RDA note  - depends on Region (Q2) only (new)</t>
+          <t xml:space="preserve">    9. Eligibility panel - RDA note  - depends on Region (Q2) only</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="12"/>
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   10. Size-gated line items         - depends on Size (Q3), layered on blocks 1 and 2 (new)</t>
+        </is>
+      </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Note: as of 2026-09-03, a sector + need combination with no matching program</t>
-        </is>
-      </c>
+      <c r="A33" s="12"/>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (block 1) shows nothing at all - the old "No stream specific to your sector"</t>
+          <t xml:space="preserve">  Note: as of 2026-09-03, a sector + need combination with no matching program</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  (block 1) shows nothing at all - the old "No stream specific to your sector"</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">  notice was removed. Those rows are marked "(nothing shown here)" below.</t>
         </is>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="12"/>
-    </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Note: block 9 is new - once any region is picked, a one-line note naming that</t>
-        </is>
-      </c>
+      <c r="A37" s="12"/>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  region's development agency (with a link) is appended at the bottom of the</t>
+          <t xml:space="preserve">  Note: block 9 - once any region is picked, a one-line note naming that region's</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Eligibility criteria panel, after the checklist and the Large Enterprise note.</t>
+          <t xml:space="preserve">  development agency (with a link) is appended at the bottom of the Eligibility</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  It does not depend on Need, Size, or Sector.</t>
+          <t xml:space="preserve">  criteria panel, after the checklist and the Large Enterprise note. It does not</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="12"/>
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  depend on Need, Size, or Sector.</t>
+        </is>
+      </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  To trace one full click-through: pick a Need + Sector row in block 1 (the main</t>
-        </is>
-      </c>
+      <c r="A42" s="12"/>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  program panel), then read the matching Need row in block 2, the matching</t>
+          <t xml:space="preserve">  Note: Question 3 (size) now has a 5th answer, "Non-profit, association, board of</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Need + Region row in block 3, the matching Sector row in block 4, block 5 as-is,</t>
+          <t xml:space="preserve">  trade" - the Regional Tariff Response Initiative is open to these too. And size</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  the matching Size row in block 7, Sector row in block 8, and Region row in block 9.</t>
+          <t xml:space="preserve">  can now hide or show individual programs within an already-visible panel, not</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Together those give everything shown on that path.</t>
+          <t xml:space="preserve">  just change eligibility badges: the Large Enterprise Tariff Loan only appears in</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="12"/>
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the Liquidity panel (block 2) for "Large enterprise", and AgriMarketing's SME vs.</t>
+        </is>
+      </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Use the Comments column here to flag routing that looks wrong (a program missing</t>
+          <t xml:space="preserve">  National Industry Association streams in the Agriculture/Transformation panel</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  or misplaced for a given selection), separate from wording issues in Content Review.</t>
+          <t xml:space="preserve">  (block 1) switch on whether "Non-profit..." was picked. Block 1 and block 2's own</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="12"/>
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  rows for those two panels now say so inline; block 10 spells out all 10 size x</t>
+        </is>
+      </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TAB: Gap Analysis</t>
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  panel combinations one at a time.</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Compares every program named on two live Canada.ca pages - the workers/employers</t>
-        </is>
-      </c>
+      <c r="A52" s="12"/>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  tariff-support page and the Canada Strong campaign page - against the CSV that</t>
+          <t xml:space="preserve">  To trace one full click-through: pick a Need + Sector row in block 1 (the main</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  drives the wizard, to catch anything the wizard is missing.</t>
+          <t xml:space="preserve">  program panel), then read the matching Need row in block 2, the matching</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1. Missing - employer/business side       - on the source page, not in the CSV</t>
+          <t xml:space="preserve">  Need + Region row in block 3, the matching Sector row in block 4, block 5 as-is,</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2. Missing - new program (not in the CSV) - Build Communities Strong Fund</t>
+          <t xml:space="preserve">  the matching Size row in block 7, Sector row in block 8, Region row in block 9,</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3. Missing - worker-facing supports        - out of scope by design: the wizard</t>
+          <t xml:space="preserve">  and - if your path touches the Liquidity or Agriculture/Transformation panels -</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                 only covers the business path, and</t>
+          <t xml:space="preserve">  your Size row in block 10. Together those give everything shown on that path.</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                                 "I am a worker" on the start page</t>
-        </is>
-      </c>
+      <c r="A59" s="12"/>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                 routes straight to that source page</t>
+          <t xml:space="preserve">  Use the Comments column here to flag routing that looks wrong (a program missing</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                 instead of building a list</t>
+          <t xml:space="preserve">  or misplaced for a given selection), separate from wording issues in Content Review.</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    4. Confirmed present                       - already in the wizard; Maps to</t>
-        </is>
-      </c>
+      <c r="A62" s="12"/>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                                 wizard program names the matching</t>
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAB: Gap Analysis</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                                 CSV / Decision Tree entry</t>
+          <t xml:space="preserve">  Compares every program named on two live Canada.ca pages - the workers/employers</t>
         </is>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Set Status per row to Add to wizard, Won't add, or leave Open for a call still</t>
+          <t xml:space="preserve">  tariff-support page and the Canada Strong campaign page - against the CSV that</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  to be made; rows already in the wizard default to Already covered.</t>
+          <t xml:space="preserve">  drives the wizard, to catch anything the wizard is missing.</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="12"/>
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1. Missing - employer/business side       - on the source page, not in the CSV</t>
+        </is>
+      </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content Review and Decision Tree tabs: set Status to Needs change if flagging</t>
+          <t xml:space="preserve">    2. Missing - new program (not in the CSV) - Build Communities Strong Fund</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">something for a fix, or Approved once happy with a row. Leave as Open otherwise.</t>
+          <t xml:space="preserve">    3. Missing - worker-facing supports        - out of scope by design: the wizard</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add your name under Reviewer on any tab.</t>
+          <t xml:space="preserve">                                                 only covers the business path, and</t>
         </is>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="12"/>
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 "I am a worker" on the start page</t>
+        </is>
+      </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Source files:</t>
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                 routes straight to that source page</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/canada_strong_en.yml</t>
+          <t xml:space="preserve">                                                 instead of building a list</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/canada_strong_fr.yml</t>
+          <t xml:space="preserve">    4. Confirmed present                       - already in the wizard; Maps to</t>
         </is>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/_data/tariff_tool_links.csv  (the program list behind the Decision Tree tab)</t>
+          <t xml:space="preserve">                                                 wizard program names the matching</t>
         </is>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  canada-strong/business-en.html  (the template that assembles the results page)</t>
+          <t xml:space="preserve">                                                 CSV / Decision Tree entry</t>
         </is>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="12"/>
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Set Status per row to Add to wizard, Won't add, or leave Open for a call still</t>
+        </is>
+      </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Compared against, for the Gap Analysis tab (checked 2026-09-03):</t>
+          <t xml:space="preserve">  to be made; rows already in the wizard default to Already covered.</t>
         </is>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  https://www.canada.ca/en/department-finance/programs/international-trade-finance-policy/</t>
-        </is>
-      </c>
+      <c r="A79" s="12"/>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    canadas-response-us-tariffs/support-canadian-workers-employers.html</t>
+          <t xml:space="preserve">Content Review and Decision Tree tabs: set Status to Needs change if flagging</t>
         </is>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">something for a fix, or Approved once happy with a row. Leave as Open otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add your name under Reviewer on any tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="12"/>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source files:</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/canada_strong_en.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/canada_strong_fr.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/_data/tariff_tool_links.csv  (the program list behind the Decision Tree tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  canada-strong/business-en.html  (the template that assembles the results page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="12"/>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Compared against, for the Gap Analysis tab (checked 2026-09-03):</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  https://www.canada.ca/en/department-finance/programs/international-trade-finance-policy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    canadas-response-us-tariffs/support-canadian-workers-employers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  https://www.canada.ca/en/campaign/canadastrong.html</t>
         </is>
@@ -659,7 +739,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2398,17 +2478,17 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-1to5m]</t>
+          <t xml:space="preserve">question-3.option[size-nonprofit]</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
+          <t xml:space="preserve">Non-profit, association, board of trade</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">De 1 à 5 millions de dollars et 3 ans ou plus d'activité</t>
+          <t xml:space="preserve">Organisme sans but lucratif, association, chambre de commerce</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -2427,17 +2507,17 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-5mplus]</t>
+          <t xml:space="preserve">question-3.option[size-1to5m]</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
+          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 millions de dollars ou plus et 10 employés à temps plein ou plus</t>
+          <t xml:space="preserve">De 1 à 5 millions de dollars et 3 ans ou plus d'activité</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -2456,17 +2536,17 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-3.option[size-large]</t>
+          <t xml:space="preserve">question-3.option[size-5mplus]</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Large enterprise</t>
+          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grande entreprise</t>
+          <t xml:space="preserve">5 millions de dollars ou plus et 10 employés à temps plein ou plus</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -2478,53 +2558,53 @@
       <c r="G62" s="2"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 3 - size</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-3.option[size-large]</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large enterprise</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grande entreprise</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F63" s="5"/>
+      <c r="G63" s="2"/>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 4 - sector</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">business.questions.question-4.legend</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 4 of 4: What is your sector and tariff impact?</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Question 4 sur 4 : Quel est votre secteur et quelle est l'incidence des droits de douane?</t>
-        </is>
-      </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F63" s="9"/>
-      <c r="G63" s="6"/>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question 4 - sector</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question-4.option[sec-forestry]</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forestry and softwood lumber</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Foresterie et bois d'œuvre</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -2543,17 +2623,17 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-steel]</t>
+          <t xml:space="preserve">question-4.option[sec-forestry]</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steel, aluminium and copper</t>
+          <t xml:space="preserve">Forestry and softwood lumber</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acier, aluminium et cuivre</t>
+          <t xml:space="preserve">Foresterie et bois d'œuvre</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -2572,17 +2652,17 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-mfg]</t>
+          <t xml:space="preserve">question-4.option[sec-steel]</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
+          <t xml:space="preserve">Steel, aluminium and copper</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabrication et autres exportateurs</t>
+          <t xml:space="preserve">Acier, aluminium et cuivre</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -2601,17 +2681,17 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-agri]</t>
+          <t xml:space="preserve">question-4.option[sec-mfg]</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+          <t xml:space="preserve">Manufacturing and other exporters</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agroalimentaire, poisson et fruits de mer</t>
+          <t xml:space="preserve">Fabrication et autres exportateurs</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -2630,17 +2710,17 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">question-4.option[sec-usexport]</t>
+          <t xml:space="preserve">question-4.option[sec-agri]</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exportations vers les États-Unis représentant 15 % ou plus de vos revenus</t>
+          <t xml:space="preserve">Agriculture, agroalimentaire, poisson et fruits de mer</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -2652,53 +2732,53 @@
       <c r="G68" s="6"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question 4 - sector</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question-4.option[sec-usexport]</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exportations vers les États-Unis représentant 15 % ou plus de vos revenus</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F69" s="9"/>
+      <c r="G69" s="6"/>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility checklist</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">business.eligibility.heading</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Critères d'admissibilité</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F69" s="5"/>
-      <c r="G69" s="2"/>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility checklist</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">business.eligibility.body</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Programs on this page commonly apply these criteria. This is a guide, not a decision - the program you apply to makes the final determination.</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les programmes de cette page appliquent couramment ces critères. Il s'agit d'un guide et non d'une décision : le programme auquel vous présentez une demande rend la décision finale.</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -2717,17 +2797,17 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[0].text (incorporation)</t>
+          <t xml:space="preserve">business.eligibility.body</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Canadian-incorporated</t>
+          <t xml:space="preserve">Programs on this page commonly apply these criteria. This is a guide, not a decision - the program you apply to makes the final determination.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Constituée en société au Canada</t>
+          <t xml:space="preserve">Les programmes de cette page appliquent couramment ces critères. Il s'agit d'un guide et non d'une décision : le programme auquel vous présentez une demande rend la décision finale.</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -2746,17 +2826,17 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[1].text (years operating)</t>
+          <t xml:space="preserve">criteria[0].text (incorporation)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 or more years operating</t>
+          <t xml:space="preserve">Canadian-incorporated</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 ans ou plus d'activité</t>
+          <t xml:space="preserve">Constituée en société au Canada</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -2775,17 +2855,17 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[2].text (revenue)</t>
+          <t xml:space="preserve">criteria[1].text (years operating)</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">$1 million or more in annual revenue</t>
+          <t xml:space="preserve">3 or more years operating</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 million de dollars ou plus de revenus annuels</t>
+          <t xml:space="preserve">3 ans ou plus d'activité</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -2804,17 +2884,17 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[3].text (cash flow)</t>
+          <t xml:space="preserve">criteria[2].text (revenue)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive cash flow</t>
+          <t xml:space="preserve">$1 million or more in annual revenue</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flux de trésorerie positif</t>
+          <t xml:space="preserve">1 million de dollars ou plus de revenus annuels</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -2833,17 +2913,17 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">criteria[4].text (US export/tariff impact)</t>
+          <t xml:space="preserve">criteria[3].text (cash flow)</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15% or more of revenue from U.S. exports, or a 10% tariff-driven revenue decline or cost increase</t>
+          <t xml:space="preserve">Positive cash flow</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 % ou plus des revenus provenant d'exportations vers les États-Unis, ou une baisse de revenus ou une hausse de coûts de 10 % attribuable aux droits de douane</t>
+          <t xml:space="preserve">Flux de trésorerie positif</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -2862,17 +2942,17 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">business.eligibility.large_note</t>
+          <t xml:space="preserve">criteria[4].text (US export/tariff impact)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">As a large enterprise, the Large Enterprise Tariff Loan (LETL) is the stream built for your size.</t>
+          <t xml:space="preserve">15% or more of revenue from U.S. exports, or a 10% tariff-driven revenue decline or cost increase</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">En tant que grande entreprise, le Crédit pour les grandes entreprises touchées par les droits de douane est le volet conçu pour votre taille.</t>
+          <t xml:space="preserve">15 % ou plus des revenus provenant d'exportations vers les États-Unis, ou une baisse de revenus ou une hausse de coûts de 10 % attribuable aux droits de douane</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -2884,53 +2964,53 @@
       <c r="G76" s="2"/>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="7" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility checklist</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">business.eligibility.large_note</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As a large enterprise, the Large Enterprise Tariff Loan (LETL) is the stream built for your size.</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En tant que grande entreprise, le Crédit pour les grandes entreprises touchées par les droits de douane est le volet conçu pour votre taille.</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F77" s="5"/>
+      <c r="G77" s="2"/>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility badges</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">badge[met] (years/revenue/US export)</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Met</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Satisfait</t>
-        </is>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="F77" s="9"/>
-      <c r="G77" s="6"/>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility badges</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badge[review] (incorporation/years/cash flow/US export)</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Needs review</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">À vérifier</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -2949,17 +3029,17 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">badge[notmet] (revenue)</t>
+          <t xml:space="preserve">badge[review] (incorporation/years/cash flow/US export)</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not met</t>
+          <t xml:space="preserve">Needs review</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non satisfait</t>
+          <t xml:space="preserve">À vérifier</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -2970,10 +3050,39 @@
       <c r="F79" s="9"/>
       <c r="G79" s="6"/>
     </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility badges</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badge[notmet] (revenue)</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not met</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non satisfait</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="F80" s="9"/>
+      <c r="G80" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G79"/>
+  <autoFilter ref="A1:G80"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E79">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E80">
       <formula1>"Open,Needs change,Approved"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2982,7 +3091,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -3789,7 +3898,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1 Need + Q4 Sector</t>
+          <t xml:space="preserve">Q1 Need + Q4 Sector (2 lines also gated by Q3 Size - see block 10)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3804,7 +3913,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">(any - 2 of these 5 lines are size-gated, see block 10)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3819,8 +3928,8 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AgriMarketing Program: Market Diversification for SMEs (AAFC)
-AgriMarketing Program: Market Diversification for National Industry Associations (AAFC)
+          <t xml:space="preserve">AgriMarketing Program: Market Diversification for SMEs (AAFC) - shown for every Q3 answer EXCEPT "Non-profit, association, board of trade"
+AgriMarketing Program: Market Diversification for National Industry Associations (AAFC) - shown ONLY for "Non-profit, association, board of trade"
 Trade Commissioner Service (agri-food) (AAFC)
 Canada Brand (AAFC)
 Single window contact for agri-food trade services (AAFC)</t>
@@ -3828,8 +3937,8 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programme Agri-marketing : Diversification des marchés pour les petites et moyennes entreprises (AAFC)
-Programme Agri-marketing : Diversification des marchés pour les associations nationales de l'industrie (AAFC)
+          <t xml:space="preserve">Programme Agri-marketing : Diversification des marchés pour les petites et moyennes entreprises (AAFC) - affiché pour toute réponse Q3 SAUF « Organisme sans but lucratif, association, chambre de commerce »
+Programme Agri-marketing : Diversification des marchés pour les associations nationales de l'industrie (AAFC) - affiché UNIQUEMENT pour « Organisme sans but lucratif, association, chambre de commerce »
 Service des délégués commerciaux (AAFC)
 Marque Canada (AAFC)
 Guichet unique pour communiquer avec le Service d'exportation agroalimentaire (AAFC)</t>
@@ -4235,7 +4344,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1 Need only (always shown)</t>
+          <t xml:space="preserve">Q1 Need only (1 line also gated by Q3 Size - see block 10)</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -4250,7 +4359,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any)</t>
+          <t xml:space="preserve">(any - 1 of these 6 lines is size-gated, see block 10)</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -4266,7 +4375,7 @@
       <c r="H23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Pivot to Grow Loan - Liquidity Support stream (BDC)
-Large Enterprise Tariff Loan (LETL) (CEEFC / CDEV)
+Large Enterprise Tariff Loan (LETL) (CEEFC / CDEV) - shown ONLY for "Large enterprise"
 Regional Tariff Response Initiative (national hub) (ISED / RDAs)
 Duties Relief Program (CBSA)
 Duty Drawback Program (CBSA)
@@ -4276,7 +4385,7 @@
       <c r="I23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Prêt Pivoter pour se propulser – volet soutien aux liquidités (BDC)
-Crédit pour les grandes entreprises touchées par les droits de douane (CGETDD) (CEEFC / CDEV)
+Crédit pour les grandes entreprises touchées par les droits de douane (CGETDD) (CEEFC / CDEV) - affiché UNIQUEMENT pour « Grande entreprise »
 Initiative régionale de réponse tarifaire (ISED / RDAs)
 Programme d'exonération des droits (CBSA)
 Programme de drawback (CBSA)
@@ -6442,240 +6551,246 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Non-profit, association, board of trade</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"3 or more years operating" badge: Needs review
+"$1 million or more in annual revenue" badge: Not met
+Large Enterprise (LETL) note: not shown
+(badges borrow size-under1m's as a placeholder - no non-profit-specific guidance yet)</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
+Insigne pour « 1 million de dollars ou plus de revenus annuels » : Non satisfait
+Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée
+(les insignes empruntent ceux de size-under1m comme choix provisoire - aucune orientation propre aux OSBL pour le moment)</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K63" s="5"/>
+      <c r="L63" s="2"/>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7. Eligibility badges by size</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size only</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"3 or more years operating" badge: Met
 "$1 million or more in annual revenue" badge: Met
 Large Enterprise (LETL) note: not shown</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : Satisfait
 Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
 Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K63" s="5"/>
-      <c r="L63" s="2"/>
-    </row>
-    <row r="64" spans="1:12">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K64" s="5"/>
+      <c r="L64" s="2"/>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Eligibility badges by size</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Q3 Size only</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"3 or more years operating" badge: Needs review
 "$1 million or more in annual revenue" badge: Met
 Large Enterprise (LETL) note: not shown</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
 Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
 Note sur le Crédit pour les grandes entreprises (CGETDD) : non affichée</t>
         </is>
       </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K64" s="5"/>
-      <c r="L64" s="2"/>
-    </row>
-    <row r="65" spans="1:12">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K65" s="5"/>
+      <c r="L65" s="2"/>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Eligibility badges by size</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Q3 Size only</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Large enterprise</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"3 or more years operating" badge: Needs review
 "$1 million or more in annual revenue" badge: Met
 Large Enterprise (LETL) note: SHOWN - "As a large enterprise, the Large Enterprise Tariff Loan (LETL) is the stream built for your size."</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Insigne pour « 3 ans ou plus d'activité » : À vérifier
 Insigne pour « 1 million de dollars ou plus de revenus annuels » : Satisfait
 Note sur le Crédit pour les grandes entreprises (CGETDD) : AFFICHÉE - « En tant que grande entreprise, le Crédit pour les grandes entreprises touchées par les droits de douane est le volet conçu pour votre taille. »</t>
         </is>
       </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K65" s="5"/>
-      <c r="L65" s="2"/>
-    </row>
-    <row r="66" spans="1:12">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K66" s="5"/>
+      <c r="L66" s="2"/>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">8. Eligibility badge by sector</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q4 Sector only</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Forestry and softwood lumber</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
-        </is>
-      </c>
-      <c r="J66" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K66" s="9"/>
-      <c r="L66" s="6"/>
-    </row>
-    <row r="67" spans="1:12">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Eligibility badge by sector</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4 Sector only</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Steel, aluminium and copper</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
@@ -6729,7 +6844,7 @@
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing and other exporters</t>
+          <t xml:space="preserve">Steel, aluminium and copper</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -6783,7 +6898,7 @@
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+          <t xml:space="preserve">Manufacturing and other exporters</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
@@ -6837,7 +6952,7 @@
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -6847,12 +6962,12 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Met</t>
+          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Needs review</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : Satisfait</t>
+          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : À vérifier</t>
         </is>
       </c>
       <c r="J70" s="9" t="inlineStr">
@@ -6864,103 +6979,103 @@
       <c r="L70" s="6"/>
     </row>
     <row r="71" spans="1:12">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Eligibility badge by sector</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q4 Sector only</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exporting to the U.S. with 15% or more of revenue from U.S. exports</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"15% or more of revenue from U.S. exports..." badge: Met</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insigne pour « 15 % ou plus des revenus provenant d'exportations vers les États-Unis... » : Satisfait</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K71" s="9"/>
+      <c r="L71" s="6"/>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Atlantic</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your regional development agency can help you: Atlantic Canada Opportunities Agency</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence de promotion économique du Canada atlantique</t>
-        </is>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
-        </is>
-      </c>
-      <c r="K71" s="5"/>
-      <c r="L71" s="2"/>
-    </row>
-    <row r="72" spans="1:12">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quebec</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(any)</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your regional development agency can help you: Canada Economic Development for Quebec Regions</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Développement économique Canada pour les régions du Québec</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
@@ -6989,7 +7104,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
+          <t xml:space="preserve">Quebec</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -7009,12 +7124,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your regional development agency can help you: Federal Economic Development Agency for Northern Ontario</t>
+          <t xml:space="preserve">Your regional development agency can help you: Canada Economic Development for Quebec Regions</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence fédérale de développement économique pour le Nord de l'Ontario</t>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Développement économique Canada pour les régions du Québec</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
@@ -7043,7 +7158,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
+          <t xml:space="preserve">Northern Ontario (including Parry Sound)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -7063,12 +7178,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your regional development agency can help you: Federal Economic Development Agency for Southern Ontario</t>
+          <t xml:space="preserve">Your regional development agency can help you: Federal Economic Development Agency for Northern Ontario</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence fédérale de développement économique pour le Sud de l'Ontario</t>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence fédérale de développement économique pour le Nord de l'Ontario</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
@@ -7097,7 +7212,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
+          <t xml:space="preserve">Southern Ontario (south of Muskoka)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -7117,12 +7232,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your regional development agency can help you: Prairies Economic Development Canada</t>
+          <t xml:space="preserve">Your regional development agency can help you: Federal Economic Development Agency for Southern Ontario</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Développement économique Canada pour les Prairies</t>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence fédérale de développement économique pour le Sud de l'Ontario</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
@@ -7151,7 +7266,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">British Columbia</t>
+          <t xml:space="preserve">Manitoba, Saskatchewan, Alberta</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -7171,12 +7286,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your regional development agency can help you: PacifiCan</t>
+          <t xml:space="preserve">Your regional development agency can help you: Prairies Economic Development Canada</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : PacifiCan</t>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Développement économique Canada pour les Prairies</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
@@ -7205,7 +7320,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The North</t>
+          <t xml:space="preserve">British Columbia</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -7225,12 +7340,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your regional development agency can help you: Canadian Northern Economic Development Agency</t>
+          <t xml:space="preserve">Your regional development agency can help you: PacifiCan</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence canadienne de développement économique du Nord</t>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : PacifiCan</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
@@ -7241,10 +7356,604 @@
       <c r="K77" s="5"/>
       <c r="L77" s="2"/>
     </row>
+    <row r="78" spans="1:12">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Eligibility panel - regional development agency note</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q2 Region only (always shown once a region is picked)</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The North</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility criteria (note appended after the checklist)</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your regional development agency can help you: Canadian Northern Economic Development Agency</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Votre agence de développement régional peut vous aider : Agence canadienne de développement économique du Nord</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K78" s="5"/>
+      <c r="L78" s="2"/>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Under $1 million in annual revenue</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any - sector-agnostic panel)</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is HIDDEN - not shown for this size.</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est MASQUÉ - non affiché pour cette taille.</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K79" s="9"/>
+      <c r="L79" s="6"/>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-profit, association, board of trade</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any - sector-agnostic panel)</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is HIDDEN - not shown for this size.</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est MASQUÉ - non affiché pour cette taille.</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K80" s="9"/>
+      <c r="L80" s="6"/>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any - sector-agnostic panel)</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is HIDDEN - not shown for this size.</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est MASQUÉ - non affiché pour cette taille.</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K81" s="9"/>
+      <c r="L81" s="6"/>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any - sector-agnostic panel)</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is HIDDEN - not shown for this size.</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est MASQUÉ - non affiché pour cette taille.</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K82" s="9"/>
+      <c r="L82" s="6"/>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity for a tariff-driven cash-flow gap</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large enterprise</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any - sector-agnostic panel)</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidity: open to all sectors (block 2)</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large Enterprise Tariff Loan (LETL) is SHOWN - this is the one size that reveals it.</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le Crédit pour les grandes entreprises (CGETDD) est AFFICHÉ - la seule taille qui le révèle.</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K83" s="9"/>
+      <c r="L83" s="6"/>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transformation or capital project</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Under $1 million in annual revenue</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgriMarketing SME stream is SHOWN. AgriMarketing NIA stream is HIDDEN.</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le volet PME d'Agri-marketing est AFFICHÉ. Le volet ANI est MASQUÉ.</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K84" s="9"/>
+      <c r="L84" s="6"/>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transformation or capital project</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-profit, association, board of trade</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgriMarketing SME stream is HIDDEN. AgriMarketing NIA stream is SHOWN - this is the one size that reveals it.</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le volet PME d'Agri-marketing est MASQUÉ. Le volet ANI est AFFICHÉ - la seule taille qui le révèle.</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K85" s="9"/>
+      <c r="L85" s="6"/>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transformation or capital project</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$1 million to $5 million and 3 or more years operating</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgriMarketing SME stream is SHOWN. AgriMarketing NIA stream is HIDDEN.</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le volet PME d'Agri-marketing est AFFICHÉ. Le volet ANI est MASQUÉ.</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K86" s="9"/>
+      <c r="L86" s="6"/>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transformation or capital project</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$5 million or more with 10 or more full-time employees</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgriMarketing SME stream is SHOWN. AgriMarketing NIA stream is HIDDEN.</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le volet PME d'Agri-marketing est AFFICHÉ. Le volet ANI est MASQUÉ.</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K87" s="9"/>
+      <c r="L87" s="6"/>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Size-gated line items within existing panels</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q3 Size, layered on top of Q1 Need + Q4 Sector (new as of the LETL/AgriMarketing size-gate update)</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transformation or capital project</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any)</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large enterprise</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture, agri-food, fish and seafood</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture: transformation and capital projects (block 1)</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AgriMarketing SME stream is SHOWN. AgriMarketing NIA stream is HIDDEN.</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le volet PME d'Agri-marketing est AFFICHÉ. Le volet ANI est MASQUÉ.</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="K88" s="9"/>
+      <c r="L88" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L77"/>
+  <autoFilter ref="A1:L88"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J88">
       <formula1>"Open,Needs change,Approved"</formula1>
     </dataValidation>
   </dataValidations>
